--- a/疲勞量表/69.xlsx
+++ b/疲勞量表/69.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="34.85546875" customWidth="1" style="12" min="1" max="1"/>
@@ -736,6 +736,98 @@
       <c r="G13" s="19" t="n"/>
       <c r="L13" s="22" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>06/10-06/16 T2實習最後一週</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="L14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>06/17-06/23 T2期末考週</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>06/24-06/30 T2結訓、行政法、訓育活動</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="L16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>07/08-07/14 安檢</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="L17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>07/08-07/14 山訓</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="21" t="n"/>
+      <c r="L18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>07/15-07/21 安檢</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="21" t="n"/>
+      <c r="L19" s="22" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:M3"/>

--- a/疲勞量表/69.xlsx
+++ b/疲勞量表/69.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="34.85546875" customWidth="1" style="12" min="1" max="1"/>
@@ -828,6 +828,208 @@
       <c r="I19" s="21" t="n"/>
       <c r="L19" s="22" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>07/22-07/28 危管&amp;凱米</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="L20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>07/29-08/04 泳訓</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>08/05-08/11 泳訓</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>08/19-08/25 泳訓</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>08/19-08/25 體適能</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="L24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>08/26-09/01 急流</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>09/02-09/08 救助訓</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>09/09-09/15 救助訓</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>09/16-09/22 救助訓</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>09/23-09/29 救助訓</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:M3"/>

--- a/疲勞量表/69.xlsx
+++ b/疲勞量表/69.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="34.85546875" customWidth="1" style="12" min="1" max="1"/>
@@ -1030,6 +1030,28 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>09/30-10/06 救助訓</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>*太累囉，週末多去休息~</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:M3"/>
